--- a/baseline1.xlsx
+++ b/baseline1.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ck\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/394a0fe494bc10a7/repos/github.com/yuzucha16/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C034038A-A34A-42F7-A994-5DA0B5354D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{C034038A-A34A-42F7-A994-5DA0B5354D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F548DEBC-A523-4B29-AFD1-95C61BD861FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{640DD344-2293-45BA-A5DC-1D44DEC369F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <r>
       <rPr>
@@ -199,17 +199,13 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
-  <si>
-    <t>N/A</t>
-    <phoneticPr fontId="1"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="181" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -302,7 +298,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -312,43 +308,37 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -363,19 +353,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -712,6 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC8C65-852C-4F4D-89FA-063D4FC1F009}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:I13"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -726,246 +717,231 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
     </row>
     <row r="3" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="18">
         <f>F5*F7</f>
         <v>800000</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="18">
         <f t="shared" ref="G4:H4" si="0">G5*G7</f>
         <v>1040000</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="18">
         <f t="shared" si="0"/>
         <v>1352000</v>
       </c>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10"/>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="19">
         <v>1000</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="20">
         <f>F5*(1+G6)</f>
         <v>1300</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="20">
         <f>G5*(1+H6)</f>
         <v>1690</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="21">
+      <c r="F6" s="19" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G6" s="19">
         <v>0.3</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="19">
         <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="10"/>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="21">
         <v>800</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="19">
         <v>800</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="19">
         <v>800</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="18">
         <f>F9+F12</f>
         <v>300000</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="18">
         <f t="shared" ref="G8:H8" si="1">G9+G12</f>
         <v>500000</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="18">
         <f t="shared" si="1"/>
         <v>700000</v>
       </c>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="10"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="20">
         <f>F11*F10</f>
         <v>200000</v>
       </c>
-      <c r="G9" s="22">
-        <f t="shared" ref="G9:H9" si="2">G11*G10</f>
+      <c r="G9" s="20">
+        <f t="shared" ref="G9" si="2">G11*G10</f>
         <v>400000</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="20">
         <v>600000</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="11" t="s">
+      <c r="B10" s="11"/>
+      <c r="D10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="19">
         <v>1</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="19">
         <v>2</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="15"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="13"/>
+      <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="19">
         <v>200000</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="19">
         <v>200000</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="19">
         <v>200000</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="10"/>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="19">
         <v>100000</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="19">
         <v>100000</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="19">
         <v>100000</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="22">
         <f>F4-F8</f>
         <v>500000</v>
       </c>
-      <c r="G13" s="24">
-        <f t="shared" ref="G13:H13" si="3">G4-G8</f>
+      <c r="G13" s="22">
+        <f t="shared" ref="G13" si="3">G4-G8</f>
         <v>540000</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="22">
         <f>H4-H8</f>
         <v>652000</v>
       </c>
-      <c r="I13" s="17"/>
+      <c r="I13" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
